--- a/assets/downloads/2026-03-20-windows-app-safe-child-process-handling-job-object-exit-propagation-stdio-watchdog-checklist.xlsx
+++ b/assets/downloads/2026-03-20-windows-app-safe-child-process-handling-job-object-exit-propagation-stdio-watchdog-checklist.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Checklist-en" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist-ja'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checklist-en'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist-ja'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checklist-en'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,11 +446,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="96" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>まず結論</t>
+          <t>Job Object ????</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>親の生死と子プロセス木の寿命を結びつけたいなら、基準点は Job Object です</t>
+          <t>Job Object ? process tree ??????????</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -510,12 +510,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>まず結論</t>
+          <t>Job Object ????</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>console への終了依頼 と プロセス木の回収 は別です 前者は process group と GenerateConsoleCtrlEvent 後者は Job Object</t>
+          <t>???????????????????? KILL_ON_JOB_CLOSE ???????</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -529,12 +529,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>まず結論</t>
+          <t>Job Object ????</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>起動時点から Job に入れたい なら、STARTUPINFOEX と PROC_THREAD_ATTRIBUTE_JOB_LIST を使う設計が素直です</t>
+          <t>BREAKAWAY ????????????</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -548,12 +548,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>まず結論</t>
+          <t>Job Object ????</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>標準出力 / 標準エラーは並列に吸い上げる のが基本です</t>
+          <t>?????? Job ???????? STARTUPINFOEX / PROC_THREAD_ATTRIBUTE_JOB_LIST ???????</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -567,12 +567,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>まず結論</t>
+          <t>Job Object ????</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>stdin を使うなら、書き終えたら close して EOF を伝える ところまで設計します</t>
+          <t>job handle ??????????????????????????</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -586,12 +586,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>まず結論</t>
+          <t>Job Object ????</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>watchdog は監視対象の Job の外に置く ほうが安全です</t>
+          <t>Job completion port ???????????????????</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>まず結論</t>
+          <t>????</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>.NET の Kill(entireProcessTree: true) は便利ですが、Windows の tree lifecycle 管理そのものではありません</t>
+          <t>??????? -&gt; timeout ?? -&gt; Job kill ????????????????</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -624,12 +624,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>やってはいけないこと</t>
+          <t>????</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Kill(entireProcessTree: true) だけで tree lifecycle が解けたと思う</t>
+          <t>GUI child ? CloseMainWindow ???????????????</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -643,12 +643,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>やってはいけないこと</t>
+          <t>????</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>bInheritHandles=TRUE のまま全部継承する</t>
+          <t>console child ? CREATE_NEW_PROCESS_GROUP ? CTRL_BREAK_EVENT ??????????</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>やってはいけないこと</t>
+          <t>????</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>stdout を全部読んでから stderr を読む</t>
+          <t>worker / headless child ?? stdin / pipe / event ????? shutdown protocol ???</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>やってはいけないこと</t>
+          <t>??????????</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>pipe の未使用 end を閉じない</t>
+          <t>stdout ? stderr ???? drain ????</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -700,12 +700,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>やってはいけないこと</t>
+          <t>??????????</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>UI thread で WaitForSingleObject(INFINITE) する</t>
+          <t>stdin ???????????? close ??EOF ??????????</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -719,12 +719,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>やってはいけないこと</t>
+          <t>??????????</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>watchdog を監視対象と同じ Job に入れる</t>
+          <t>??????? pipe end ??????</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>やってはいけないこと</t>
+          <t>??????????</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>259 を普通の exit code に使う</t>
+          <t>????????????? UseShellExecute=false ????????? handle ???????</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -757,12 +757,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>やってはいけないこと</t>
+          <t>watchdog ???</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Job completion port の通知を唯一の真実にする</t>
+          <t>watchdog / restart authority ?????? Job ????????</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>watchdog ???</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>tree cleanup の基準点は Job Object</t>
+          <t>exit ??? polling ???? wait handle ??????????</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -795,12 +795,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>watchdog ???</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>graceful shutdown は GUI / console / worker で分ける</t>
+          <t>hang ????????? heartbeat / progress / health probe ??????</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -814,12 +814,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>watchdog ???</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>stdio は並列 drain と EOF まで含めて設計する</t>
+          <t>restart policy ? backoff ??????????????</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -833,19 +833,38 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>???????</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>watchdog は監視対象の外に置き、polling ではなく wait handle と heartbeat で見る CreateProcess や Process.Start 自体は入口にすぎません。 本当に事故率に効くのは、終了責任の所在 と I/O の流し切り です。</t>
+          <t>Kill(entireProcessTree: true) ??????? lifecycle ????????</t>
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>UI thread ? message pump thread ? WaitForSingleObject(INFINITE) ???????</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -856,11 +875,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="96" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
@@ -901,12 +920,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The short answer</t>
+          <t>Job Object / ownership</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>if you want the lifetime of the child-process tree tied to the parent's lifetime, the main baseline is Job Objects</t>
+          <t>Job Objects are used as the containment boundary for the process tree</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -920,12 +939,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The short answer</t>
+          <t>Job Object / ownership</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>requesting a console child to exit and reclaiming a process tree are different jobs the first is about process groups and GenerateConsoleCtrlEvent the second is about Job Objects</t>
+          <t>KILL_ON_JOB_CLOSE is configured when child-tree cleanup must follow parent exit</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -939,12 +958,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The short answer</t>
+          <t>Job Object / ownership</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>if you want a child placed into a Job from the moment it starts, STARTUPINFOEX plus PROC_THREAD_ATTRIBUTE_JOB_LIST is the clean design</t>
+          <t>BREAKAWAY is not enabled without a deliberate reason</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -958,12 +977,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The short answer</t>
+          <t>Job Object / ownership</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>standard output and standard error should normally be drained in parallel</t>
+          <t>Children that must join the Job from process birth use STARTUPINFOEX / PROC_THREAD_ATTRIBUTE_JOB_LIST</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -977,12 +996,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The short answer</t>
+          <t>Job Object / ownership</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>if you use stdin, closing it to send EOF is part of the shutdown design</t>
+          <t>The final owner of the job handle is defined, and accidental inheritance or duplication is prevented</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -996,12 +1015,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The short answer</t>
+          <t>Job Object / ownership</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>the watchdog should usually live outside the Job of the process it watches</t>
+          <t>Job completion port notifications are not treated as the only source of truth</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -1015,12 +1034,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The short answer</t>
+          <t>Shutdown design</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>.NET Kill(entireProcessTree: true) is useful, but it is not the same thing as designing process-tree lifecycle correctly</t>
+          <t>Shutdown follows a sequence of graceful request -&gt; timeout -&gt; Job kill</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -1034,12 +1053,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Things not to do</t>
+          <t>Shutdown design</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>assume Kill(entireProcessTree: true) alone solves process-tree lifecycle</t>
+          <t>GUI children are asked to exit gracefully through CloseMainWindow or an equivalent first</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -1053,12 +1072,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Things not to do</t>
+          <t>Shutdown design</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>leave bInheritHandles=TRUE wide open</t>
+          <t>Console children are designed around CREATE_NEW_PROCESS_GROUP and CTRL_BREAK_EVENT</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -1072,12 +1091,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Things not to do</t>
+          <t>Shutdown design</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>read all of stdout and only then start reading stderr</t>
+          <t>Worker or headless children have a dedicated shutdown protocol such as stdin, pipe, or event signaling</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -1091,12 +1110,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Things not to do</t>
+          <t>Stdio / handles</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>keep unused pipe ends open</t>
+          <t>stdout and stderr are drained in parallel</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -1110,12 +1129,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Things not to do</t>
+          <t>Stdio / handles</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>block a UI thread with WaitForSingleObject(INFINITE)</t>
+          <t>When stdin is used, it is closed after writing so EOF is delivered explicitly</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -1129,12 +1148,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Things not to do</t>
+          <t>Stdio / handles</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>place the watchdog in the same Job as the worker tree</t>
+          <t>Unused pipe ends are closed in both parent and child sides</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -1148,12 +1167,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Things not to do</t>
+          <t>Stdio / handles</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>use 259 as an ordinary application exit code</t>
+          <t>When standard streams are redirected, UseShellExecute=false or tightly scoped handle inheritance is enforced</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -1167,12 +1186,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Things not to do</t>
+          <t>Watchdog / monitoring</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>treat Job completion port notifications as the only truth source</t>
+          <t>The watchdog or restart authority lives outside the monitored Job</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1186,12 +1205,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Wrap-up</t>
+          <t>Watchdog / monitoring</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Job Objects are the baseline for tree cleanup</t>
+          <t>Exit monitoring is designed around wait handles rather than polling loops</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -1205,12 +1224,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Wrap-up</t>
+          <t>Watchdog / monitoring</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>graceful shutdown should differ for GUI, console, and worker-style children</t>
+          <t>If hang detection matters, heartbeat, progress, or health-probe signals exist</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -1224,12 +1243,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Wrap-up</t>
+          <t>Watchdog / monitoring</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>stdio design must include parallel draining and EOF behavior</t>
+          <t>Restart policy includes backoff and restart-count limits</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -1243,19 +1262,38 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Wrap-up</t>
+          <t>Avoidance</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>watchdogs belong outside the monitored tree and should use wait handles plus heartbeat where needed CreateProcess and Process.Start are only the entrance. The part that really reduces incidents is lifecycle ownership plus I/O completion discipline.</t>
+          <t>Lifecycle management does not rely only on Kill(entireProcessTree: true)</t>
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Avoidance</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>UI threads or message-pump threads are not blocked with WaitForSingleObject(INFINITE)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/assets/downloads/2026-03-20-windows-app-safe-child-process-handling-job-object-exit-propagation-stdio-watchdog-checklist.xlsx
+++ b/assets/downloads/2026-03-20-windows-app-safe-child-process-handling-job-object-exit-propagation-stdio-watchdog-checklist.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Job Object ????</t>
+          <t>Job Object / 所有権</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Job Object ? process tree ??????????</t>
+          <t>プロセス木の管理境界として Job Object を使う</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -510,12 +510,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Job Object ????</t>
+          <t>Job Object / 所有権</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>???????????????????? KILL_ON_JOB_CLOSE ???????</t>
+          <t>親の終了に合わせて子プロセス木を確実に回収したいなら、KILL_ON_JOB_CLOSE を設定する</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -529,12 +529,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Job Object ????</t>
+          <t>Job Object / 所有権</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BREAKAWAY ????????????</t>
+          <t>明確な意図がない限り、BREAKAWAY を有効にしない</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -548,12 +548,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Job Object ????</t>
+          <t>Job Object / 所有権</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>?????? Job ???????? STARTUPINFOEX / PROC_THREAD_ATTRIBUTE_JOB_LIST ???????</t>
+          <t>起動時点から Job に所属させたい子は、STARTUPINFOEX / PROC_THREAD_ATTRIBUTE_JOB_LIST で作成する</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -567,12 +567,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Job Object ????</t>
+          <t>Job Object / 所有権</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>job handle ??????????????????????????</t>
+          <t>job handle の最終所有者を決め、意図しない継承や複製を防ぐ</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -586,12 +586,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Job Object ????</t>
+          <t>Job Object / 所有権</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Job completion port ???????????????????</t>
+          <t>Job completion port の通知だけを唯一の真実として扱わない</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>終了設計</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>??????? -&gt; timeout ?? -&gt; Job kill ????????????????</t>
+          <t>終了処理は「協調終了の依頼 -&gt; timeout 待ち -&gt; Job kill」の順で設計する</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -624,12 +624,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>終了設計</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>GUI child ? CloseMainWindow ???????????????</t>
+          <t>GUI 子プロセスは、まず CloseMainWindow 相当で穏やかな終了を依頼する</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -643,12 +643,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>終了設計</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>console child ? CREATE_NEW_PROCESS_GROUP ? CTRL_BREAK_EVENT ??????????</t>
+          <t>console 子プロセスは、CREATE_NEW_PROCESS_GROUP と CTRL_BREAK_EVENT を前提に設計する</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>終了設計</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>worker / headless child ?? stdin / pipe / event ????? shutdown protocol ???</t>
+          <t>worker / headless child には、stdin / pipe / event など専用の shutdown protocol を用意する</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>標準入出力 / handle</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>stdout ? stderr ???? drain ????</t>
+          <t>stdout と stderr は並列に drain する</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -700,12 +700,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>標準入出力 / handle</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>stdin ???????????? close ??EOF ??????????</t>
+          <t>stdin を使うなら、書き込み後に close して EOF を明示的に伝える</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -719,12 +719,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>標準入出力 / handle</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>??????? pipe end ??????</t>
+          <t>親側・子側ともに未使用の pipe end を閉じる</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>標準入出力 / handle</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>????????????? UseShellExecute=false ????????? handle ???????</t>
+          <t>標準入出力をリダイレクトするなら、UseShellExecute=false か、厳密に絞った handle 継承にする</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -757,12 +757,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>watchdog ???</t>
+          <t>watchdog / 監視</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>watchdog / restart authority ?????? Job ????????</t>
+          <t>watchdog や restart authority は、監視対象の Job の外に置く</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>watchdog ???</t>
+          <t>watchdog / 監視</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>exit ??? polling ???? wait handle ??????????</t>
+          <t>終了監視は polling loop ではなく wait handle ベースで組む</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -795,12 +795,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>watchdog ???</t>
+          <t>watchdog / 監視</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>hang ????????? heartbeat / progress / health probe ??????</t>
+          <t>hang 検知が必要なら、heartbeat / progress / health probe などの信号を持つ</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -814,12 +814,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>watchdog ???</t>
+          <t>watchdog / 監視</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>restart policy ? backoff ??????????????</t>
+          <t>restart policy には backoff と再起動回数の上限を入れる</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -833,12 +833,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>???????</t>
+          <t>避けたい実装</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Kill(entireProcessTree: true) ??????? lifecycle ????????</t>
+          <t>Kill(entireProcessTree: true) だけに lifecycle 管理を依存させない</t>
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
@@ -852,12 +852,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>???????</t>
+          <t>避けたい実装</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>UI thread ? message pump thread ? WaitForSingleObject(INFINITE) ???????</t>
+          <t>UI thread や message pump thread を WaitForSingleObject(INFINITE) で止めない</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
